--- a/Dialog/Drama/sorin.xlsx
+++ b/Dialog/Drama/sorin.xlsx
@@ -1,114 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Steam\steamapps\common\Elin\Package\_Lang_Vietnamese\Lang\VN\Dialog\Drama\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2BBBA0-283A-4540-AA8A-A4682CFAF945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="13656" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="sorin" sheetId="1" r:id="rId1"/>
+    <sheet name="sorin" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>step</t>
-  </si>
-  <si>
-    <t>jump</t>
-  </si>
-  <si>
-    <t>if</t>
-  </si>
-  <si>
-    <t>if2</t>
-  </si>
-  <si>
-    <t>action</t>
-  </si>
-  <si>
-    <t>param</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>text_JP</t>
-  </si>
-  <si>
-    <t>text_EN</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>何です？ もちろん、僕を煩わせるほどの重要な話なんでしょうね？</t>
-  </si>
-  <si>
-    <t>What is it? I assume it’s important enough to warrant disturbing me.</t>
-  </si>
-  <si>
-    <t>inject</t>
-  </si>
-  <si>
-    <t>Unique</t>
-  </si>
-  <si>
-    <t>choice/bye</t>
-  </si>
-  <si>
-    <t>cancel</t>
-  </si>
-  <si>
-    <t>Chuyện gì thế? Ta đoán rằng đó hẳn phải là một chuyện cực kỳ quan trọng thì ngươi mới dám làm phiền ta thế này chứ nhỉ?</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t xml:space="preserve">step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">param</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text_JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text_EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何です？ もちろん、僕を煩わせるほどの重要な話なんでしょうね？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is it? I assume it’s important enough to warrant disturbing me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice/bye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Chuyện gì thế? Ta đoán rằng đó hẳn phải là một chuyện cực kỳ quan trọng thì ngươi mới dám làm phiền ta thế này chứ nhỉ?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -148,21 +158,60 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -173,13 +222,12 @@
         <charset val="128"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -238,78 +286,62 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -362,111 +394,112 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="21.21875" customWidth="1"/>
-    <col min="4" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" customWidth="1"/>
-    <col min="8" max="9" width="7.109375" customWidth="1"/>
-    <col min="10" max="10" width="60.77734375" customWidth="1"/>
-    <col min="11" max="11" width="53.21875" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1" ht="12.8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="I2">
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
         <f>MAX(I4:I1048576)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="B5" t="s">
+    <row r="5" ht="12.8">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
+    <row r="7" ht="12.8">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="I8">
+    <row r="8" ht="12.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
+      <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="E10" t="s">
+    <row r="10" ht="12.8">
+      <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="E11" t="s">
+    <row r="11" ht="12.8">
+      <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -474,7 +507,12 @@
   <conditionalFormatting sqref="I4:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>